--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>84.30282483870681</v>
+        <v>13.69920903628986</v>
       </c>
       <c r="D2" t="n">
-        <v>82.45222766772829</v>
+        <v>13.39848699600585</v>
       </c>
       <c r="E2" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F2" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.21460685958413</v>
+        <v>1.822373614682421</v>
       </c>
       <c r="D3" t="n">
-        <v>11.2429135993327</v>
+        <v>1.826973459891564</v>
       </c>
       <c r="E3" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F3" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>68.60166640545178</v>
+        <v>11.14777079088591</v>
       </c>
       <c r="D4" t="n">
-        <v>66.57717409544065</v>
+        <v>10.81879079050911</v>
       </c>
       <c r="E4" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F4" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>72.6723912936822</v>
+        <v>11.80926358522336</v>
       </c>
       <c r="D5" t="n">
-        <v>70.7685524872977</v>
+        <v>11.49988977918588</v>
       </c>
       <c r="E5" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F5" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>63.17851971671607</v>
+        <v>10.26650945396636</v>
       </c>
       <c r="D6" t="n">
-        <v>61.14668651796252</v>
+        <v>9.936336559168909</v>
       </c>
       <c r="E6" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F6" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>70.57507603730437</v>
+        <v>11.46844985606196</v>
       </c>
       <c r="D7" t="n">
-        <v>68.82688352491623</v>
+        <v>11.18436857279889</v>
       </c>
       <c r="E7" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F7" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.7876665212273</v>
+        <v>7.927995809699437</v>
       </c>
       <c r="D8" t="n">
-        <v>47.22718683991312</v>
+        <v>7.674417861485882</v>
       </c>
       <c r="E8" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F8" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>58.35310758916365</v>
+        <v>9.482379983239094</v>
       </c>
       <c r="D9" t="n">
-        <v>56.87869139185512</v>
+        <v>9.242787351176457</v>
       </c>
       <c r="E9" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F9" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>52.86480588879699</v>
+        <v>8.590530956929511</v>
       </c>
       <c r="D10" t="n">
-        <v>52.92338452351497</v>
+        <v>8.600049985071182</v>
       </c>
       <c r="E10" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F10" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>56.42240057622276</v>
+        <v>9.168640093636197</v>
       </c>
       <c r="D11" t="n">
-        <v>56.91108289860774</v>
+        <v>9.248050971023758</v>
       </c>
       <c r="E11" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F11" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>54.27975217925012</v>
+        <v>8.820459729128146</v>
       </c>
       <c r="D12" t="n">
-        <v>33.96212728068797</v>
+        <v>5.518845683111796</v>
       </c>
       <c r="E12" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F12" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>61.90506512064437</v>
+        <v>10.05957308210471</v>
       </c>
       <c r="D13" t="n">
-        <v>61.56937922261429</v>
+        <v>10.00502412367482</v>
       </c>
       <c r="E13" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F13" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>62.56194924916456</v>
+        <v>10.16631675298924</v>
       </c>
       <c r="D14" t="n">
-        <v>45.94407799128345</v>
+        <v>7.465912673583561</v>
       </c>
       <c r="E14" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F14" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>69.81728730373889</v>
+        <v>11.34530918685757</v>
       </c>
       <c r="D15" t="n">
-        <v>63.71187942799139</v>
+        <v>10.3531804070486</v>
       </c>
       <c r="E15" t="n">
-        <v>16.16248900769808</v>
+        <v>2.626404463750938</v>
       </c>
       <c r="F15" t="n">
-        <v>16.8780682835655</v>
+        <v>2.742686096079395</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
